--- a/applications/MICROSAMPLING_study/positive/pos_lipid_reference_set.xlsx
+++ b/applications/MICROSAMPLING_study/positive/pos_lipid_reference_set.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10531"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10830"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/pilot_study/positive/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/saralondonoosorio/Documents/GitHub/CEMBIO-EURAC/applications/MICROSAMPLING_study/positive/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{65ED97DA-8F68-4348-A226-B4792989AA95}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5BA5C87-1A4C-584D-9F6B-9DC7BDB93772}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="660" windowWidth="14720" windowHeight="17400" xr2:uid="{9E5E902E-872A-BE45-A1A9-54571E2C3B45}"/>
   </bookViews>
@@ -41,9 +41,6 @@
     <t>CAR (5:0)</t>
   </si>
   <si>
-    <t>LPC (20:0)</t>
-  </si>
-  <si>
     <t>SM</t>
   </si>
   <si>
@@ -113,9 +110,6 @@
     <t>Cer</t>
   </si>
   <si>
-    <t>ISTD</t>
-  </si>
-  <si>
     <t>C17 Sphinganine</t>
   </si>
   <si>
@@ -140,12 +134,6 @@
     <t>HexCer(d18:1/24:0)</t>
   </si>
   <si>
-    <t>LysoPC (18:1(d7))</t>
-  </si>
-  <si>
-    <t>LysoPE (18:1(d7))</t>
-  </si>
-  <si>
     <t>PG (15:0/18:1(d7))</t>
   </si>
   <si>
@@ -164,9 +152,6 @@
     <t>TG(15:0/18:1(d7))/15:0)</t>
   </si>
   <si>
-    <t>Chol Ester (18:1(d7))</t>
-  </si>
-  <si>
     <t>Endogenous</t>
   </si>
   <si>
@@ -183,6 +168,21 @@
   </si>
   <si>
     <t>LPC_1</t>
+  </si>
+  <si>
+    <t>LPC(20:0)</t>
+  </si>
+  <si>
+    <t>CE(18:1(d7))</t>
+  </si>
+  <si>
+    <t>LPC(18:1(d7))</t>
+  </si>
+  <si>
+    <t>LPE(18:1(d7))</t>
+  </si>
+  <si>
+    <t>IS</t>
   </si>
 </sst>
 </file>
@@ -629,27 +629,27 @@
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="C1" s="7" t="s">
+        <v>10</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C1" s="7" t="s">
-        <v>11</v>
-      </c>
-      <c r="D1" s="2" t="s">
+      <c r="E1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E1" s="7" t="s">
-        <v>9</v>
-      </c>
       <c r="F1" s="7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B2" s="3" t="s">
         <v>0</v>
@@ -665,17 +665,17 @@
         <v>48</v>
       </c>
       <c r="F2" s="9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="H2" s="5"/>
       <c r="I2" s="5"/>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A3" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C3" s="8">
         <v>496.33980000000003</v>
@@ -688,17 +688,17 @@
         <v>153.6</v>
       </c>
       <c r="F3" s="9" t="s">
-        <v>48</v>
+        <v>43</v>
       </c>
       <c r="H3" s="5"/>
       <c r="I3" s="5"/>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A4" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>1</v>
+        <v>44</v>
       </c>
       <c r="C4" s="8">
         <v>552.40239999999994</v>
@@ -707,21 +707,21 @@
         <v>4.24</v>
       </c>
       <c r="E4" s="9">
-        <f>D4*60</f>
+        <f t="shared" ref="E4:E10" si="1">D4*60</f>
         <v>254.4</v>
       </c>
       <c r="F4" s="9" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="H4" s="5"/>
       <c r="I4" s="5"/>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A5" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="C5" s="8">
         <v>701.55920000000003</v>
@@ -730,21 +730,21 @@
         <v>6.19</v>
       </c>
       <c r="E5" s="9">
-        <f>D5*60</f>
+        <f t="shared" si="1"/>
         <v>371.40000000000003</v>
       </c>
       <c r="F5" s="9" t="s">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H5" s="5"/>
       <c r="I5" s="5"/>
     </row>
     <row r="6" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A6" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C6" s="8">
         <v>758.56939999999997</v>
@@ -753,21 +753,21 @@
         <v>7.76</v>
       </c>
       <c r="E6" s="9">
-        <f>D6*60</f>
+        <f t="shared" si="1"/>
         <v>465.59999999999997</v>
       </c>
       <c r="F6" s="9" t="s">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H6" s="5"/>
       <c r="I6" s="5"/>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="C7" s="8">
         <v>759.63879999999995</v>
@@ -776,21 +776,21 @@
         <v>11.43</v>
       </c>
       <c r="E7" s="9">
-        <f>D7*60</f>
+        <f t="shared" si="1"/>
         <v>685.8</v>
       </c>
       <c r="F7" s="9" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="H7" s="5"/>
       <c r="I7" s="5"/>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="8">
         <v>812.69740000000002</v>
@@ -799,21 +799,21 @@
         <v>12.25</v>
       </c>
       <c r="E8" s="9">
-        <f>D8*60</f>
+        <f t="shared" si="1"/>
         <v>735</v>
       </c>
       <c r="F8" s="9" t="s">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="H8" s="5"/>
       <c r="I8" s="5"/>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="C9" s="8">
         <v>900.80150000000003</v>
@@ -822,21 +822,21 @@
         <v>13.97</v>
       </c>
       <c r="E9" s="9">
-        <f>D9*60</f>
+        <f t="shared" si="1"/>
         <v>838.2</v>
       </c>
       <c r="F9" s="9" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="H9" s="5"/>
       <c r="I9" s="5"/>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C10" s="8">
         <v>880.83274340259902</v>
@@ -845,21 +845,21 @@
         <v>16.05</v>
       </c>
       <c r="E10" s="9">
-        <f>D10*60</f>
+        <f t="shared" si="1"/>
         <v>963</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>47</v>
+        <v>42</v>
       </c>
       <c r="H10" s="5"/>
       <c r="I10" s="5"/>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="3" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C11" s="9">
         <v>678.65070000000003</v>
@@ -871,17 +871,17 @@
         <v>720</v>
       </c>
       <c r="F11" s="9" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H11" s="5"/>
       <c r="I11" s="5"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B12" s="10" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="C12" s="11">
         <v>759.58749999999998</v>
@@ -894,17 +894,17 @@
         <v>387.6</v>
       </c>
       <c r="F12" s="13" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="H12" s="5"/>
       <c r="I12" s="5"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B13" s="10" t="s">
-        <v>37</v>
+        <v>33</v>
       </c>
       <c r="C13" s="11">
         <v>738.64700000000005</v>
@@ -917,17 +917,17 @@
         <v>436.26</v>
       </c>
       <c r="F13" s="13" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="H13" s="5"/>
       <c r="I13" s="5"/>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B14" s="10" t="s">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="C14" s="11">
         <v>753.61339999999996</v>
@@ -940,17 +940,17 @@
         <v>490.26</v>
       </c>
       <c r="F14" s="13" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="H14" s="5"/>
       <c r="I14" s="5"/>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B15" s="10" t="s">
-        <v>39</v>
+        <v>35</v>
       </c>
       <c r="C15" s="11">
         <v>711.56640000000004</v>
@@ -963,17 +963,17 @@
         <v>510.18</v>
       </c>
       <c r="F15" s="13" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="H15" s="5"/>
       <c r="I15" s="5"/>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B16" s="10" t="s">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="C16" s="11">
         <v>605.58439999999996</v>
@@ -986,17 +986,17 @@
         <v>700.8</v>
       </c>
       <c r="F16" s="13" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="H16" s="5"/>
       <c r="I16" s="5"/>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B17" s="10" t="s">
-        <v>41</v>
+        <v>37</v>
       </c>
       <c r="C17" s="11">
         <v>829.79849999999999</v>
@@ -1009,17 +1009,17 @@
         <v>839.88</v>
       </c>
       <c r="F17" s="13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="H17" s="5"/>
       <c r="I17" s="5"/>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B18" s="10" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C18" s="11">
         <v>675.67790000000002</v>
@@ -1032,17 +1032,17 @@
         <v>927.6</v>
       </c>
       <c r="F18" s="13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="H18" s="5"/>
       <c r="I18" s="5"/>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B19" s="10" t="s">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="C19" s="11">
         <v>529.39940000000001</v>
@@ -1055,15 +1055,15 @@
         <v>164.57999999999998</v>
       </c>
       <c r="F19" s="13" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="10" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B20" s="10" t="s">
-        <v>35</v>
+        <v>47</v>
       </c>
       <c r="C20" s="11">
         <v>487.35239999999999</v>
@@ -1076,15 +1076,15 @@
         <v>170.88</v>
       </c>
       <c r="F20" s="13" t="s">
-        <v>46</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="3" t="s">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="C21" s="9">
         <v>288.28969999999998</v>
@@ -1096,7 +1096,7 @@
         <v>119.4</v>
       </c>
       <c r="F21" s="9" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
     </row>
   </sheetData>
